--- a/scripts_data_misc/SDM Power Bypass Temperature Modeling Results.xlsx
+++ b/scripts_data_misc/SDM Power Bypass Temperature Modeling Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kleinschmidtgroup-my.sharepoint.com/personal/vanessa_martinez_kleinschmidtgroup_com/Documents/ARG Modeling/2025 Modeling/Sept SDM Modeling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/avaisvil_usbr_gov/Documents/Documents/R/american_river_SDM/scripts_data_misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="8_{B659F4CB-8F8C-4C7C-97FA-406A38135EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{644A392D-03F7-4048-8309-29457E945F27}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{B659F4CB-8F8C-4C7C-97FA-406A38135EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E5C1F0A-118A-44F3-9C51-362D0B548C56}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="18" windowWidth="20130" windowHeight="13728" xr2:uid="{DA9C8022-DC09-4000-A3A9-95D660C1C697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{DA9C8022-DC09-4000-A3A9-95D660C1C697}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario Summary" sheetId="5" r:id="rId1"/>
@@ -340,13 +340,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28486,10 +28486,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -28808,15 +28804,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB45341-B330-4CED-860C-044F70C9C215}">
   <dimension ref="B1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.68359375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.15625" customWidth="1"/>
-    <col min="4" max="4" width="16.20703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
@@ -28827,7 +28823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>4</v>
       </c>
@@ -28838,98 +28834,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>Flow!M73</f>
         <v>10147.5</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>Flow!N73</f>
         <v>32175</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>Flow!O73</f>
         <v>40095</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>Flow!P73</f>
         <v>37125</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>Flow!Q73</f>
         <v>17325</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>Flow!R73</f>
         <v>20790</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>Flow!S73</f>
         <v>17325</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>Flow!T73</f>
         <v>30096</v>
       </c>
@@ -28944,52 +28940,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2252E231-6044-439D-8F1A-64267922AA19}">
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.62890625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="15"/>
       <c r="E2" t="s">
         <v>5</v>
       </c>
@@ -29039,7 +29034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45922</v>
       </c>
@@ -29106,7 +29101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45923</v>
       </c>
@@ -29173,7 +29168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45924</v>
       </c>
@@ -29240,7 +29235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45925</v>
       </c>
@@ -29307,7 +29302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45926</v>
       </c>
@@ -29374,7 +29369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45927</v>
       </c>
@@ -29441,7 +29436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45928</v>
       </c>
@@ -29508,7 +29503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45929</v>
       </c>
@@ -29575,7 +29570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45930</v>
       </c>
@@ -29642,7 +29637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45931</v>
       </c>
@@ -29712,7 +29707,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45932</v>
       </c>
@@ -29782,7 +29777,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45933</v>
       </c>
@@ -29852,7 +29847,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45934</v>
       </c>
@@ -29922,7 +29917,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45935</v>
       </c>
@@ -29992,7 +29987,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45936</v>
       </c>
@@ -30062,7 +30057,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45937</v>
       </c>
@@ -30132,7 +30127,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45938</v>
       </c>
@@ -30202,7 +30197,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45939</v>
       </c>
@@ -30272,7 +30267,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45940</v>
       </c>
@@ -30342,7 +30337,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45941</v>
       </c>
@@ -30412,7 +30407,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45942</v>
       </c>
@@ -30482,7 +30477,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45943</v>
       </c>
@@ -30552,7 +30547,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45944</v>
       </c>
@@ -30622,7 +30617,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45945</v>
       </c>
@@ -30692,7 +30687,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45946</v>
       </c>
@@ -30762,7 +30757,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45947</v>
       </c>
@@ -30832,7 +30827,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45948</v>
       </c>
@@ -30902,7 +30897,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45949</v>
       </c>
@@ -30972,7 +30967,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45950</v>
       </c>
@@ -31042,7 +31037,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45951</v>
       </c>
@@ -31112,7 +31107,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45952</v>
       </c>
@@ -31182,7 +31177,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45953</v>
       </c>
@@ -31252,7 +31247,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45954</v>
       </c>
@@ -31322,7 +31317,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45955</v>
       </c>
@@ -31392,7 +31387,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45956</v>
       </c>
@@ -31462,7 +31457,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45957</v>
       </c>
@@ -31532,7 +31527,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45958</v>
       </c>
@@ -31602,7 +31597,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45959</v>
       </c>
@@ -31672,7 +31667,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45960</v>
       </c>
@@ -31742,7 +31737,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45961</v>
       </c>
@@ -31812,7 +31807,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45962</v>
       </c>
@@ -31882,7 +31877,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -31952,7 +31947,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45964</v>
       </c>
@@ -32022,7 +32017,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45965</v>
       </c>
@@ -32092,7 +32087,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45966</v>
       </c>
@@ -32162,7 +32157,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45967</v>
       </c>
@@ -32232,7 +32227,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45968</v>
       </c>
@@ -32302,7 +32297,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45969</v>
       </c>
@@ -32372,7 +32367,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45970</v>
       </c>
@@ -32442,7 +32437,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45971</v>
       </c>
@@ -32512,7 +32507,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45972</v>
       </c>
@@ -32582,7 +32577,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45973</v>
       </c>
@@ -32652,7 +32647,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45974</v>
       </c>
@@ -32722,7 +32717,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45975</v>
       </c>
@@ -32792,7 +32787,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45976</v>
       </c>
@@ -32862,7 +32857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45977</v>
       </c>
@@ -32932,7 +32927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45978</v>
       </c>
@@ -33002,7 +32997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45979</v>
       </c>
@@ -33072,7 +33067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -33142,7 +33137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45981</v>
       </c>
@@ -33212,7 +33207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45982</v>
       </c>
@@ -33282,7 +33277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45983</v>
       </c>
@@ -33352,7 +33347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45984</v>
       </c>
@@ -33422,7 +33417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45985</v>
       </c>
@@ -33492,7 +33487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45986</v>
       </c>
@@ -33562,7 +33557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45987</v>
       </c>
@@ -33632,7 +33627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45988</v>
       </c>
@@ -33702,7 +33697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45989</v>
       </c>
@@ -33772,7 +33767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45990</v>
       </c>
@@ -33842,7 +33837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45991</v>
       </c>
@@ -33912,132 +33907,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="M73" s="14">
-        <f>SUM(M3:M72)</f>
+      <c r="M73" s="13">
+        <f t="shared" ref="M73:T73" si="17">SUM(M3:M72)</f>
         <v>10147.5</v>
       </c>
-      <c r="N73" s="15">
-        <f>SUM(N3:N72)</f>
+      <c r="N73" s="14">
+        <f t="shared" si="17"/>
         <v>32175</v>
       </c>
-      <c r="O73" s="15">
-        <f>SUM(O3:O72)</f>
+      <c r="O73" s="14">
+        <f t="shared" si="17"/>
         <v>40095</v>
       </c>
-      <c r="P73" s="15">
-        <f>SUM(P3:P72)</f>
+      <c r="P73" s="14">
+        <f t="shared" si="17"/>
         <v>37125</v>
       </c>
-      <c r="Q73" s="15">
-        <f>SUM(Q3:Q72)</f>
+      <c r="Q73" s="14">
+        <f t="shared" si="17"/>
         <v>17325</v>
       </c>
-      <c r="R73" s="15">
-        <f>SUM(R3:R72)</f>
+      <c r="R73" s="14">
+        <f t="shared" si="17"/>
         <v>20790</v>
       </c>
-      <c r="S73" s="15">
-        <f>SUM(S3:S72)</f>
+      <c r="S73" s="14">
+        <f t="shared" si="17"/>
         <v>17325</v>
       </c>
-      <c r="T73" s="15">
-        <f>SUM(T3:T72)</f>
+      <c r="T73" s="14">
+        <f t="shared" si="17"/>
         <v>30096</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
     </row>
   </sheetData>
@@ -34056,50 +34051,50 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800B54B0-EA7C-4926-B0FE-A38A4E0CF372}">
   <dimension ref="A1:V104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="15"/>
+      <c r="K1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="11"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -34167,7 +34162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45922</v>
       </c>
@@ -34236,7 +34231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45923</v>
       </c>
@@ -34305,7 +34300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45924</v>
       </c>
@@ -34374,7 +34369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45925</v>
       </c>
@@ -34443,7 +34438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45926</v>
       </c>
@@ -34512,7 +34507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45927</v>
       </c>
@@ -34581,7 +34576,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45928</v>
       </c>
@@ -34650,7 +34645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45929</v>
       </c>
@@ -34719,7 +34714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45930</v>
       </c>
@@ -34788,7 +34783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45931</v>
       </c>
@@ -34857,7 +34852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45932</v>
       </c>
@@ -34926,7 +34921,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45933</v>
       </c>
@@ -34995,7 +34990,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45934</v>
       </c>
@@ -35064,7 +35059,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45935</v>
       </c>
@@ -35133,7 +35128,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45936</v>
       </c>
@@ -35202,7 +35197,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45937</v>
       </c>
@@ -35271,7 +35266,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45938</v>
       </c>
@@ -35340,7 +35335,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45939</v>
       </c>
@@ -35409,7 +35404,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45940</v>
       </c>
@@ -35478,7 +35473,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45941</v>
       </c>
@@ -35547,7 +35542,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45942</v>
       </c>
@@ -35616,7 +35611,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45943</v>
       </c>
@@ -35685,7 +35680,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45944</v>
       </c>
@@ -35754,7 +35749,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45945</v>
       </c>
@@ -35823,7 +35818,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45946</v>
       </c>
@@ -35892,7 +35887,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45947</v>
       </c>
@@ -35961,7 +35956,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45948</v>
       </c>
@@ -36030,7 +36025,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45949</v>
       </c>
@@ -36099,7 +36094,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45950</v>
       </c>
@@ -36168,7 +36163,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45951</v>
       </c>
@@ -36237,7 +36232,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45952</v>
       </c>
@@ -36306,7 +36301,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45953</v>
       </c>
@@ -36375,7 +36370,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45954</v>
       </c>
@@ -36444,7 +36439,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45955</v>
       </c>
@@ -36513,7 +36508,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45956</v>
       </c>
@@ -36582,7 +36577,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45957</v>
       </c>
@@ -36651,7 +36646,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45958</v>
       </c>
@@ -36720,7 +36715,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45959</v>
       </c>
@@ -36789,7 +36784,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45960</v>
       </c>
@@ -36858,7 +36853,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45961</v>
       </c>
@@ -36927,7 +36922,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45962</v>
       </c>
@@ -36996,7 +36991,7 @@
         <v>18.333333333333332</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -37065,7 +37060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45964</v>
       </c>
@@ -37134,7 +37129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45965</v>
       </c>
@@ -37203,7 +37198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45966</v>
       </c>
@@ -37272,7 +37267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45967</v>
       </c>
@@ -37341,7 +37336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45968</v>
       </c>
@@ -37410,7 +37405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45969</v>
       </c>
@@ -37479,7 +37474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45970</v>
       </c>
@@ -37548,7 +37543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45971</v>
       </c>
@@ -37617,7 +37612,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45972</v>
       </c>
@@ -37686,7 +37681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45973</v>
       </c>
@@ -37755,7 +37750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45974</v>
       </c>
@@ -37824,7 +37819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45975</v>
       </c>
@@ -37893,7 +37888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45976</v>
       </c>
@@ -37962,7 +37957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45977</v>
       </c>
@@ -38031,7 +38026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45978</v>
       </c>
@@ -38100,7 +38095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45979</v>
       </c>
@@ -38169,7 +38164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -38238,7 +38233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45981</v>
       </c>
@@ -38307,7 +38302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45982</v>
       </c>
@@ -38376,7 +38371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45983</v>
       </c>
@@ -38445,7 +38440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45984</v>
       </c>
@@ -38514,7 +38509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45985</v>
       </c>
@@ -38583,7 +38578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45986</v>
       </c>
@@ -38652,7 +38647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45987</v>
       </c>
@@ -38721,7 +38716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45988</v>
       </c>
@@ -38790,7 +38785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45989</v>
       </c>
@@ -38859,7 +38854,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45990</v>
       </c>
@@ -38928,7 +38923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45991</v>
       </c>
@@ -38997,7 +38992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="U73">
         <v>59</v>
@@ -39007,97 +39002,97 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
     </row>
   </sheetData>
@@ -39120,50 +39115,50 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965AF274-541A-4886-982E-68F6419FAE1E}">
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="15"/>
+      <c r="K1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="11"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -39225,7 +39220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45922</v>
       </c>
@@ -39287,7 +39282,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45923</v>
       </c>
@@ -39349,7 +39344,7 @@
         <v>19.670000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45924</v>
       </c>
@@ -39411,7 +39406,7 @@
         <v>19.350000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45925</v>
       </c>
@@ -39473,7 +39468,7 @@
         <v>19.22</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45926</v>
       </c>
@@ -39535,7 +39530,7 @@
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45927</v>
       </c>
@@ -39597,7 +39592,7 @@
         <v>19.04</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45928</v>
       </c>
@@ -39659,7 +39654,7 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45929</v>
       </c>
@@ -39721,7 +39716,7 @@
         <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45930</v>
       </c>
@@ -39783,7 +39778,7 @@
         <v>16.02</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45931</v>
       </c>
@@ -39845,7 +39840,7 @@
         <v>16.68</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45932</v>
       </c>
@@ -39907,7 +39902,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45933</v>
       </c>
@@ -39969,7 +39964,7 @@
         <v>17.18</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45934</v>
       </c>
@@ -40031,7 +40026,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45935</v>
       </c>
@@ -40093,7 +40088,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45936</v>
       </c>
@@ -40155,7 +40150,7 @@
         <v>17.940000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45937</v>
       </c>
@@ -40217,7 +40212,7 @@
         <v>17.71</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45938</v>
       </c>
@@ -40279,7 +40274,7 @@
         <v>17.63</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45939</v>
       </c>
@@ -40341,7 +40336,7 @@
         <v>17.66</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45940</v>
       </c>
@@ -40403,7 +40398,7 @@
         <v>17.68</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45941</v>
       </c>
@@ -40465,7 +40460,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45942</v>
       </c>
@@ -40527,7 +40522,7 @@
         <v>18.059999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45943</v>
       </c>
@@ -40589,7 +40584,7 @@
         <v>17.809999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45944</v>
       </c>
@@ -40651,7 +40646,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45945</v>
       </c>
@@ -40713,7 +40708,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45946</v>
       </c>
@@ -40775,7 +40770,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45947</v>
       </c>
@@ -40837,7 +40832,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45948</v>
       </c>
@@ -40899,7 +40894,7 @@
         <v>17.39</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45949</v>
       </c>
@@ -40961,7 +40956,7 @@
         <v>17.37</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45950</v>
       </c>
@@ -41023,7 +41018,7 @@
         <v>17.36</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45951</v>
       </c>
@@ -41085,7 +41080,7 @@
         <v>17.010000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45952</v>
       </c>
@@ -41147,7 +41142,7 @@
         <v>16.760000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45953</v>
       </c>
@@ -41209,7 +41204,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45954</v>
       </c>
@@ -41271,7 +41266,7 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45955</v>
       </c>
@@ -41333,7 +41328,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45956</v>
       </c>
@@ -41395,7 +41390,7 @@
         <v>16.71</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45957</v>
       </c>
@@ -41457,7 +41452,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45958</v>
       </c>
@@ -41519,7 +41514,7 @@
         <v>16.559999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45959</v>
       </c>
@@ -41581,7 +41576,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45960</v>
       </c>
@@ -41643,7 +41638,7 @@
         <v>16.96</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45961</v>
       </c>
@@ -41705,7 +41700,7 @@
         <v>16.39</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45962</v>
       </c>
@@ -41767,7 +41762,7 @@
         <v>15.86</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -41829,7 +41824,7 @@
         <v>15.64</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45964</v>
       </c>
@@ -41891,7 +41886,7 @@
         <v>15.52</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45965</v>
       </c>
@@ -41953,7 +41948,7 @@
         <v>15.74</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45966</v>
       </c>
@@ -42015,7 +42010,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45967</v>
       </c>
@@ -42077,7 +42072,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45968</v>
       </c>
@@ -42139,7 +42134,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45969</v>
       </c>
@@ -42201,7 +42196,7 @@
         <v>16.170000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45970</v>
       </c>
@@ -42263,7 +42258,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45971</v>
       </c>
@@ -42325,7 +42320,7 @@
         <v>15.91</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45972</v>
       </c>
@@ -42387,7 +42382,7 @@
         <v>15.68</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45973</v>
       </c>
@@ -42449,7 +42444,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45974</v>
       </c>
@@ -42511,7 +42506,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45975</v>
       </c>
@@ -42573,7 +42568,7 @@
         <v>16.21</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45976</v>
       </c>
@@ -42635,7 +42630,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45977</v>
       </c>
@@ -42697,7 +42692,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45978</v>
       </c>
@@ -42759,7 +42754,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45979</v>
       </c>
@@ -42821,7 +42816,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -42883,7 +42878,7 @@
         <v>16.14</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45981</v>
       </c>
@@ -42945,7 +42940,7 @@
         <v>16.05</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45982</v>
       </c>
@@ -43007,7 +43002,7 @@
         <v>15.95</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45983</v>
       </c>
@@ -43069,7 +43064,7 @@
         <v>15.96</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45984</v>
       </c>
@@ -43131,7 +43126,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45985</v>
       </c>
@@ -43193,7 +43188,7 @@
         <v>15.32</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45986</v>
       </c>
@@ -43255,7 +43250,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45987</v>
       </c>
@@ -43317,7 +43312,7 @@
         <v>15.47</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45988</v>
       </c>
@@ -43379,7 +43374,7 @@
         <v>15.53</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45989</v>
       </c>
@@ -43441,7 +43436,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45990</v>
       </c>
@@ -43503,7 +43498,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45991</v>
       </c>
@@ -43565,100 +43560,100 @@
         <v>15.18</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
     </row>
   </sheetData>
@@ -43681,50 +43676,50 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5372AD56-F359-44E1-8267-920715FC8339}">
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="15"/>
+      <c r="K1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="11"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -43786,7 +43781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45922</v>
       </c>
@@ -43848,7 +43843,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45923</v>
       </c>
@@ -43910,7 +43905,7 @@
         <v>18.82</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45924</v>
       </c>
@@ -43972,7 +43967,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45925</v>
       </c>
@@ -44034,7 +44029,7 @@
         <v>18.440000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45926</v>
       </c>
@@ -44096,7 +44091,7 @@
         <v>19.11</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45927</v>
       </c>
@@ -44158,7 +44153,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45928</v>
       </c>
@@ -44220,7 +44215,7 @@
         <v>19.010000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45929</v>
       </c>
@@ -44282,7 +44277,7 @@
         <v>17.47</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45930</v>
       </c>
@@ -44344,7 +44339,7 @@
         <v>17.309999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45931</v>
       </c>
@@ -44406,7 +44401,7 @@
         <v>17.29</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45932</v>
       </c>
@@ -44468,7 +44463,7 @@
         <v>16.809999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45933</v>
       </c>
@@ -44530,7 +44525,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45934</v>
       </c>
@@ -44592,7 +44587,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45935</v>
       </c>
@@ -44654,7 +44649,7 @@
         <v>17.66</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45936</v>
       </c>
@@ -44716,7 +44711,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45937</v>
       </c>
@@ -44778,7 +44773,7 @@
         <v>18.329999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45938</v>
       </c>
@@ -44840,7 +44835,7 @@
         <v>17.88</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45939</v>
       </c>
@@ -44902,7 +44897,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45940</v>
       </c>
@@ -44964,7 +44959,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45941</v>
       </c>
@@ -45026,7 +45021,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45942</v>
       </c>
@@ -45088,7 +45083,7 @@
         <v>17.690000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45943</v>
       </c>
@@ -45150,7 +45145,7 @@
         <v>17.579999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45944</v>
       </c>
@@ -45212,7 +45207,7 @@
         <v>17.420000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45945</v>
       </c>
@@ -45274,7 +45269,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45946</v>
       </c>
@@ -45336,7 +45331,7 @@
         <v>17.190000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45947</v>
       </c>
@@ -45398,7 +45393,7 @@
         <v>17.260000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45948</v>
       </c>
@@ -45460,7 +45455,7 @@
         <v>17.22</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45949</v>
       </c>
@@ -45522,7 +45517,7 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45950</v>
       </c>
@@ -45584,7 +45579,7 @@
         <v>16.73</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45951</v>
       </c>
@@ -45646,7 +45641,7 @@
         <v>16.52</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45952</v>
       </c>
@@ -45708,7 +45703,7 @@
         <v>16.510000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45953</v>
       </c>
@@ -45770,7 +45765,7 @@
         <v>16.73</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45954</v>
       </c>
@@ -45832,7 +45827,7 @@
         <v>16.87</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45955</v>
       </c>
@@ -45894,7 +45889,7 @@
         <v>16.96</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45956</v>
       </c>
@@ -45956,7 +45951,7 @@
         <v>16.95</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45957</v>
       </c>
@@ -46018,7 +46013,7 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45958</v>
       </c>
@@ -46080,7 +46075,7 @@
         <v>16.57</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45959</v>
       </c>
@@ -46142,7 +46137,7 @@
         <v>16.36</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45960</v>
       </c>
@@ -46204,7 +46199,7 @@
         <v>15.98</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45961</v>
       </c>
@@ -46266,7 +46261,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45962</v>
       </c>
@@ -46328,7 +46323,7 @@
         <v>15.62</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -46390,7 +46385,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45964</v>
       </c>
@@ -46452,7 +46447,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45965</v>
       </c>
@@ -46514,7 +46509,7 @@
         <v>15.37</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45966</v>
       </c>
@@ -46576,7 +46571,7 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45967</v>
       </c>
@@ -46638,7 +46633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45968</v>
       </c>
@@ -46700,7 +46695,7 @@
         <v>14.89</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45969</v>
       </c>
@@ -46762,7 +46757,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45970</v>
       </c>
@@ -46824,7 +46819,7 @@
         <v>15.67</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45971</v>
       </c>
@@ -46886,7 +46881,7 @@
         <v>15.34</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45972</v>
       </c>
@@ -46948,7 +46943,7 @@
         <v>14.99</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45973</v>
       </c>
@@ -47010,7 +47005,7 @@
         <v>14.96</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45974</v>
       </c>
@@ -47072,7 +47067,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45975</v>
       </c>
@@ -47134,7 +47129,7 @@
         <v>15.71</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45976</v>
       </c>
@@ -47196,7 +47191,7 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45977</v>
       </c>
@@ -47258,7 +47253,7 @@
         <v>16.149999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45978</v>
       </c>
@@ -47320,7 +47315,7 @@
         <v>15.65</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45979</v>
       </c>
@@ -47382,7 +47377,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -47444,7 +47439,7 @@
         <v>15.28</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45981</v>
       </c>
@@ -47506,7 +47501,7 @@
         <v>15.71</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45982</v>
       </c>
@@ -47568,7 +47563,7 @@
         <v>15.52</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45983</v>
       </c>
@@ -47630,7 +47625,7 @@
         <v>15.76</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45984</v>
       </c>
@@ -47692,7 +47687,7 @@
         <v>15.78</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45985</v>
       </c>
@@ -47754,7 +47749,7 @@
         <v>15.85</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45986</v>
       </c>
@@ -47816,7 +47811,7 @@
         <v>15.71</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45987</v>
       </c>
@@ -47878,7 +47873,7 @@
         <v>15.59</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45988</v>
       </c>
@@ -47940,7 +47935,7 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45989</v>
       </c>
@@ -48002,7 +47997,7 @@
         <v>14.77</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45990</v>
       </c>
@@ -48064,7 +48059,7 @@
         <v>14.51</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45991</v>
       </c>
@@ -48126,100 +48121,100 @@
         <v>14.58</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
     </row>
   </sheetData>
@@ -48242,50 +48237,50 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4F1CB5-EBBD-46E4-8D95-B1EB4CFBDB06}">
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11" t="s">
+      <c r="J1" s="15"/>
+      <c r="K1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="11"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="T1" s="15"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -48347,7 +48342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45922</v>
       </c>
@@ -48409,7 +48404,7 @@
         <v>19.059999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45923</v>
       </c>
@@ -48471,7 +48466,7 @@
         <v>18.62</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45924</v>
       </c>
@@ -48533,7 +48528,7 @@
         <v>18.190000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45925</v>
       </c>
@@ -48595,7 +48590,7 @@
         <v>17.850000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45926</v>
       </c>
@@ -48657,7 +48652,7 @@
         <v>18.22</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45927</v>
       </c>
@@ -48719,7 +48714,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45928</v>
       </c>
@@ -48781,7 +48776,7 @@
         <v>16.309999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45929</v>
       </c>
@@ -48843,7 +48838,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45930</v>
       </c>
@@ -48905,7 +48900,7 @@
         <v>16.54</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45931</v>
       </c>
@@ -48967,7 +48962,7 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>45932</v>
       </c>
@@ -49029,7 +49024,7 @@
         <v>17.41</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>45933</v>
       </c>
@@ -49091,7 +49086,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>45934</v>
       </c>
@@ -49153,7 +49148,7 @@
         <v>17.68</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>45935</v>
       </c>
@@ -49215,7 +49210,7 @@
         <v>17.79</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>45936</v>
       </c>
@@ -49277,7 +49272,7 @@
         <v>17.87</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>45937</v>
       </c>
@@ -49339,7 +49334,7 @@
         <v>17.77</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>45938</v>
       </c>
@@ -49401,7 +49396,7 @@
         <v>17.45</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>45939</v>
       </c>
@@ -49463,7 +49458,7 @@
         <v>17.510000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45940</v>
       </c>
@@ -49525,7 +49520,7 @@
         <v>17.66</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45941</v>
       </c>
@@ -49587,7 +49582,7 @@
         <v>17.829999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45942</v>
       </c>
@@ -49649,7 +49644,7 @@
         <v>17.809999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>45943</v>
       </c>
@@ -49711,7 +49706,7 @@
         <v>18.04</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>45944</v>
       </c>
@@ -49773,7 +49768,7 @@
         <v>18.03</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>45945</v>
       </c>
@@ -49835,7 +49830,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>45946</v>
       </c>
@@ -49897,7 +49892,7 @@
         <v>17.63</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>45947</v>
       </c>
@@ -49959,7 +49954,7 @@
         <v>17.670000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>45948</v>
       </c>
@@ -50021,7 +50016,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>45949</v>
       </c>
@@ -50083,7 +50078,7 @@
         <v>17.670000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>45950</v>
       </c>
@@ -50145,7 +50140,7 @@
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>45951</v>
       </c>
@@ -50207,7 +50202,7 @@
         <v>17.47</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45952</v>
       </c>
@@ -50269,7 +50264,7 @@
         <v>17.079999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45953</v>
       </c>
@@ -50331,7 +50326,7 @@
         <v>16.78</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45954</v>
       </c>
@@ -50393,7 +50388,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45955</v>
       </c>
@@ -50455,7 +50450,7 @@
         <v>16.809999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45956</v>
       </c>
@@ -50517,7 +50512,7 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45957</v>
       </c>
@@ -50579,7 +50574,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45958</v>
       </c>
@@ -50641,7 +50636,7 @@
         <v>16.55</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45959</v>
       </c>
@@ -50703,7 +50698,7 @@
         <v>16.47</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45960</v>
       </c>
@@ -50765,7 +50760,7 @@
         <v>16.41</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45961</v>
       </c>
@@ -50827,7 +50822,7 @@
         <v>16.21</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45962</v>
       </c>
@@ -50889,7 +50884,7 @@
         <v>16.11</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45963</v>
       </c>
@@ -50951,7 +50946,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45964</v>
       </c>
@@ -51013,7 +51008,7 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45965</v>
       </c>
@@ -51075,7 +51070,7 @@
         <v>15.91</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45966</v>
       </c>
@@ -51137,7 +51132,7 @@
         <v>16.14</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45967</v>
       </c>
@@ -51199,7 +51194,7 @@
         <v>15.61</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45968</v>
       </c>
@@ -51261,7 +51256,7 @@
         <v>15.23</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45969</v>
       </c>
@@ -51323,7 +51318,7 @@
         <v>14.91</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45970</v>
       </c>
@@ -51385,7 +51380,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45971</v>
       </c>
@@ -51447,7 +51442,7 @@
         <v>14.54</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45972</v>
       </c>
@@ -51509,7 +51504,7 @@
         <v>14.55</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45973</v>
       </c>
@@ -51571,7 +51566,7 @@
         <v>14.44</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45974</v>
       </c>
@@ -51633,7 +51628,7 @@
         <v>14.65</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45975</v>
       </c>
@@ -51695,7 +51690,7 @@
         <v>15.23</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45976</v>
       </c>
@@ -51757,7 +51752,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45977</v>
       </c>
@@ -51819,7 +51814,7 @@
         <v>15.66</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45978</v>
       </c>
@@ -51881,7 +51876,7 @@
         <v>15.81</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45979</v>
       </c>
@@ -51943,7 +51938,7 @@
         <v>15.96</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45980</v>
       </c>
@@ -52005,7 +52000,7 @@
         <v>15.55</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45981</v>
       </c>
@@ -52067,7 +52062,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45982</v>
       </c>
@@ -52129,7 +52124,7 @@
         <v>14.71</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45983</v>
       </c>
@@ -52191,7 +52186,7 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>45984</v>
       </c>
@@ -52253,7 +52248,7 @@
         <v>14.81</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>45985</v>
       </c>
@@ -52315,7 +52310,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>45986</v>
       </c>
@@ -52377,7 +52372,7 @@
         <v>14.76</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>45987</v>
       </c>
@@ -52439,7 +52434,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>45988</v>
       </c>
@@ -52501,7 +52496,7 @@
         <v>14.45</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>45989</v>
       </c>
@@ -52563,7 +52558,7 @@
         <v>14.37</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>45990</v>
       </c>
@@ -52625,7 +52620,7 @@
         <v>14.02</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>45991</v>
       </c>
@@ -52687,100 +52682,100 @@
         <v>14.05</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
     </row>
   </sheetData>
@@ -52802,6 +52797,7 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" enabled="0" method="" siteId="{0693b5ba-4b18-4d7b-9341-f32f400a5494}" removed="1"/>
   <clbl:label id="{adc6e70c-c575-40a4-9676-24da4a1fdce9}" enabled="0" method="" siteId="{adc6e70c-c575-40a4-9676-24da4a1fdce9}" removed="1"/>
 </clbl:labelList>
 </file>